--- a/data/fmsForecastOutput/File1/RPT_RPT6586846416173UX_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT6586846416173UX_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>432.4379596572089</v>
+        <v>432.4379596572086</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>464.7927072399157</v>
+        <v>464.7927072399156</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>501.127342723767</v>
+        <v>501.1273427237669</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>565.3430834368205</v>
+        <v>565.3430834368204</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>609.0701680022855</v>
+        <v>609.0701680022852</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>432.4379596572089</v>
+        <v>432.4379596572086</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>464.7927072399157</v>
+        <v>464.7927072399156</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>501.127342723767</v>
+        <v>501.1273427237669</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>565.3430834368205</v>
+        <v>565.3430834368204</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>609.0701680022855</v>
+        <v>609.0701680022852</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>6991163.605504232</v>
+        <v>6991163.605504228</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>8251720.235268116</v>
+        <v>8251720.235268112</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>9532002.037715925</v>
+        <v>9532002.037715923</v>
       </c>
       <c r="P8" s="152" t="n">
         <v>10982291.06910312</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>12651186.59529066</v>
+        <v>12651186.59529065</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>537.8761566660817</v>
+        <v>537.8761566660814</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>578.1197266188276</v>
+        <v>578.1197266188274</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>623.3135715426382</v>
+        <v>623.3135715426381</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>703.1865684450902</v>
+        <v>703.1865684450898</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>757.5753094495318</v>
+        <v>757.5753094495313</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>537.8761566660817</v>
+        <v>537.8761566660814</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>578.1197266188276</v>
+        <v>578.1197266188274</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>623.3135715426382</v>
+        <v>623.3135715426381</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>703.1865684450902</v>
+        <v>703.1865684450898</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>757.5753094495318</v>
+        <v>757.5753094495313</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>6991163.605504232</v>
+        <v>6991163.605504228</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>8251720.235268116</v>
+        <v>8251720.235268112</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>9532002.037715925</v>
+        <v>9532002.037715923</v>
       </c>
       <c r="AG8" s="152" t="n">
         <v>10982291.06910312</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>12651186.59529066</v>
+        <v>12651186.59529065</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>850.1973778349499</v>
+        <v>850.1973778349501</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>934.0355079180465</v>
+        <v>934.0355079180463</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>1012.131908980887</v>
@@ -2037,10 +2037,10 @@
         <v>1373.153184967183</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>850.1973778349499</v>
+        <v>850.1973778349501</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>934.0355079180465</v>
+        <v>934.0355079180463</v>
       </c>
       <c r="J9" s="156" t="n">
         <v>1012.131908980887</v>
@@ -2052,10 +2052,10 @@
         <v>1373.153184967183</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>2838769.588989773</v>
+        <v>2838769.588989774</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>3330538.594564932</v>
+        <v>3330538.594564931</v>
       </c>
       <c r="O9" s="159" t="n">
         <v>3839684.092561611</v>
@@ -2064,7 +2064,7 @@
         <v>4291577.145252227</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>4960557.363794521</v>
+        <v>4960557.36379452</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         <v>1668.789147334074</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>2838769.588989773</v>
+        <v>2838769.588989774</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>3330538.594564932</v>
+        <v>3330538.594564931</v>
       </c>
       <c r="AF9" s="159" t="n">
         <v>3839684.092561611</v>
@@ -2114,7 +2114,7 @@
         <v>4291577.145252227</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>4960557.363794521</v>
+        <v>4960557.36379452</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,43 +2170,43 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>503.9489151402576</v>
+        <v>503.9489151402574</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>543.2757340150918</v>
+        <v>543.2757340150916</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>586.0975987253335</v>
+        <v>586.0975987253333</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>670.2864413607683</v>
+        <v>670.2864413607681</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>722.2710712217655</v>
+        <v>722.2710712217654</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>503.9489151402576</v>
+        <v>503.9489151402574</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>543.2757340150918</v>
+        <v>543.2757340150916</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>586.0975987253335</v>
+        <v>586.0975987253333</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>670.2864413607683</v>
+        <v>670.2864413607681</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>722.2710712217655</v>
+        <v>722.2710712217654</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>9829933.194494003</v>
+        <v>9829933.194494</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>11582258.82983305</v>
+        <v>11582258.82983304</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>13371686.13027754</v>
+        <v>13371686.13027753</v>
       </c>
       <c r="P10" s="165" t="n">
         <v>15273868.21435535</v>
@@ -2220,43 +2220,43 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>624.3146790854313</v>
+        <v>624.3146790854311</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>673.0962459684138</v>
+        <v>673.0962459684134</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>726.167304931834</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>830.8409369310742</v>
+        <v>830.840936931074</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>895.2639266661731</v>
+        <v>895.2639266661729</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>624.3146790854313</v>
+        <v>624.3146790854311</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>673.0962459684138</v>
+        <v>673.0962459684134</v>
       </c>
       <c r="AA10" s="162" t="n">
         <v>726.167304931834</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>830.8409369310742</v>
+        <v>830.840936931074</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>895.2639266661731</v>
+        <v>895.2639266661729</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>9829933.194494003</v>
+        <v>9829933.194494</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>11582258.82983305</v>
+        <v>11582258.82983304</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>13371686.13027754</v>
+        <v>13371686.13027753</v>
       </c>
       <c r="AG10" s="165" t="n">
         <v>15273868.21435535</v>
@@ -2330,7 +2330,7 @@
         <v>1466.06445973549</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1556.954463953512</v>
+        <v>1556.954463953511</v>
       </c>
       <c r="H11" s="155" t="n">
         <v>1146.584218233141</v>
@@ -2345,7 +2345,7 @@
         <v>1466.06445973549</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>1556.954463953512</v>
+        <v>1556.954463953511</v>
       </c>
       <c r="M11" s="158" t="n">
         <v>108106.8571842359</v>
@@ -2354,7 +2354,7 @@
         <v>129616.800929974</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>154240.2556528655</v>
+        <v>154240.2556528654</v>
       </c>
       <c r="P11" s="159" t="n">
         <v>183163.8028321264</v>
@@ -2371,7 +2371,7 @@
         <v>1173.476385398523</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1287.543819457519</v>
+        <v>1287.54381945752</v>
       </c>
       <c r="V11" s="156" t="n">
         <v>1383.728377617657</v>
@@ -2386,7 +2386,7 @@
         <v>1173.476385398523</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1287.543819457519</v>
+        <v>1287.54381945752</v>
       </c>
       <c r="AA11" s="156" t="n">
         <v>1383.728377617657</v>
@@ -2404,7 +2404,7 @@
         <v>129616.800929974</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>154240.2556528655</v>
+        <v>154240.2556528654</v>
       </c>
       <c r="AG11" s="159" t="n">
         <v>183163.8028321264</v>
@@ -2461,40 +2461,40 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>507.0403037421377</v>
+        <v>507.0403037421374</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>546.713389187268</v>
+        <v>546.7133891872678</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>589.9084012692883</v>
+        <v>589.9084012692882</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>674.6256976161477</v>
+        <v>674.6256976161476</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>727.1131365197093</v>
+        <v>727.113136519709</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>507.0403037421377</v>
+        <v>507.0403037421374</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>546.713389187268</v>
+        <v>546.7133891872678</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>589.9084012692883</v>
+        <v>589.9084012692882</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>674.6256976161477</v>
+        <v>674.6256976161476</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>727.1131365197093</v>
+        <v>727.113136519709</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>9938040.05167824</v>
+        <v>9938040.051678237</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>11711875.63076302</v>
+        <v>11711875.63076301</v>
       </c>
       <c r="O12" s="165" t="n">
         <v>13525926.3859304</v>
@@ -2503,7 +2503,7 @@
         <v>15457032.01718747</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>17833264.31252256</v>
+        <v>17833264.31252255</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,40 +2511,40 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>627.5091464158569</v>
+        <v>627.5091464158567</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>676.6700821127254</v>
+        <v>676.670082112725</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>730.1238168665362</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>835.2580030712617</v>
+        <v>835.2580030712614</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>900.1633433245684</v>
+        <v>900.1633433245681</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>627.5091464158569</v>
+        <v>627.5091464158567</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>676.6700821127254</v>
+        <v>676.670082112725</v>
       </c>
       <c r="AA12" s="162" t="n">
         <v>730.1238168665362</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>835.2580030712617</v>
+        <v>835.2580030712614</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>900.1633433245684</v>
+        <v>900.1633433245681</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>9938040.05167824</v>
+        <v>9938040.051678237</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>11711875.63076302</v>
+        <v>11711875.63076301</v>
       </c>
       <c r="AF12" s="165" t="n">
         <v>13525926.3859304</v>
@@ -2553,7 +2553,7 @@
         <v>15457032.01718747</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>17833264.31252256</v>
+        <v>17833264.31252255</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,46 +2603,46 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>399.6626302689378</v>
+        <v>399.6626302689377</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>427.5048334963496</v>
+        <v>427.5048334963494</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>457.2955618843289</v>
+        <v>457.2955618843288</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>485.0962084785712</v>
+        <v>485.096208478571</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>519.2994662553102</v>
+        <v>519.2994662553101</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>399.6626302689378</v>
+        <v>399.6626302689377</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>427.5048334963496</v>
+        <v>427.5048334963494</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>457.2955618843289</v>
+        <v>457.2955618843288</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>485.0962084785712</v>
+        <v>485.096208478571</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>519.2994662553102</v>
+        <v>519.2994662553101</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>473.1275733846854</v>
+        <v>473.1275733846852</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>519.2357478844262</v>
+        <v>519.2357478844261</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>572.2978514001064</v>
+        <v>572.2978514001062</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>619.4015956114472</v>
+        <v>619.4015956114471</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>676.5219606551991</v>
@@ -2653,46 +2653,46 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>357.5437328094592</v>
+        <v>357.5437328094591</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>382.4517540194224</v>
+        <v>382.4517540194222</v>
       </c>
       <c r="V13" s="156" t="n">
         <v>409.1029528662681</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>433.9737969357606</v>
+        <v>433.9737969357604</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>464.5725057805438</v>
+        <v>464.5725057805436</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>357.5437328094592</v>
+        <v>357.5437328094591</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>382.4517540194224</v>
+        <v>382.4517540194222</v>
       </c>
       <c r="AA13" s="156" t="n">
         <v>409.1029528662681</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>433.9737969357606</v>
+        <v>433.9737969357604</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>464.5725057805438</v>
+        <v>464.5725057805436</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>473.1275733846854</v>
+        <v>473.1275733846852</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>519.2357478844262</v>
+        <v>519.2357478844261</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>572.2978514001064</v>
+        <v>572.2978514001062</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>619.4015956114472</v>
+        <v>619.4015956114471</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>676.5219606551991</v>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>507.0338186788887</v>
+        <v>507.0338186788885</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>546.7066308537919</v>
+        <v>546.7066308537916</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>589.9011635029073</v>
+        <v>589.9011635029071</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>674.6151359167378</v>
+        <v>674.6151359167375</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>727.1020986258919</v>
+        <v>727.1020986258915</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>507.0338186788887</v>
+        <v>507.0338186788885</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>546.7066308537919</v>
+        <v>546.7066308537916</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>589.9011635029073</v>
+        <v>589.9011635029071</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>674.6151359167378</v>
+        <v>674.6151359167375</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>727.1020986258919</v>
+        <v>727.1020986258915</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>9938513.179251624</v>
+        <v>9938513.179251621</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>11712394.86651091</v>
+        <v>11712394.8665109</v>
       </c>
       <c r="O14" s="171" t="n">
         <v>13526498.6837818</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>15457651.41878309</v>
+        <v>15457651.41878308</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>17833940.83448321</v>
+        <v>17833940.8344832</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>627.4865915499436</v>
+        <v>627.4865915499433</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>676.6470053911901</v>
+        <v>676.6470053911897</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>730.0995776006229</v>
+        <v>730.0995776006228</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>835.2270558312133</v>
+        <v>835.2270558312129</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>900.1313274266755</v>
+        <v>900.1313274266751</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>627.4865915499436</v>
+        <v>627.4865915499433</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>676.6470053911901</v>
+        <v>676.6470053911897</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>730.0995776006229</v>
+        <v>730.0995776006228</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>835.2270558312133</v>
+        <v>835.2270558312129</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>900.1313274266755</v>
+        <v>900.1313274266751</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>9938513.179251624</v>
+        <v>9938513.179251621</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>11712394.86651091</v>
+        <v>11712394.8665109</v>
       </c>
       <c r="AF14" s="171" t="n">
         <v>13526498.6837818</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>15457651.41878309</v>
+        <v>15457651.41878308</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>17833940.83448321</v>
+        <v>17833940.8344832</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -4408,40 +4408,40 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>442.6509216134133</v>
+        <v>442.6509216134131</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>486.7333462292817</v>
+        <v>486.7333462292814</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>527.9550045796612</v>
+        <v>527.9550045796611</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>605.4667008589785</v>
+        <v>605.4667008589782</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>654.1532519168433</v>
+        <v>654.1532519168429</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>442.6509216134133</v>
+        <v>442.6509216134131</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>486.7333462292817</v>
+        <v>486.7333462292814</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>527.9550045796612</v>
+        <v>527.9550045796611</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>605.4667008589785</v>
+        <v>605.4667008589782</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>654.1532519168433</v>
+        <v>654.1532519168429</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>7156275.123441312</v>
+        <v>7156275.123441308</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>8641244.450909069</v>
+        <v>8641244.450909065</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>10042294.14448388</v>
@@ -4450,7 +4450,7 @@
         <v>11761727.94236721</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>13587621.40503507</v>
+        <v>13587621.40503506</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,40 +4458,40 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>550.5792707255752</v>
+        <v>550.5792707255749</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>605.4099917559422</v>
+        <v>605.409991755942</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>656.6824267255278</v>
+        <v>656.6824267255276</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>753.0932351671283</v>
+        <v>753.093235167128</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>813.6506732446965</v>
+        <v>813.650673244696</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>550.5792707255752</v>
+        <v>550.5792707255749</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>605.4099917559422</v>
+        <v>605.409991755942</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>656.6824267255278</v>
+        <v>656.6824267255276</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>753.0932351671283</v>
+        <v>753.093235167128</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>813.6506732446965</v>
+        <v>813.650673244696</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>7156275.123441312</v>
+        <v>7156275.123441308</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>8641244.450909069</v>
+        <v>8641244.450909065</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>10042294.14448388</v>
@@ -4500,7 +4500,7 @@
         <v>11761727.94236721</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>13587621.40503507</v>
+        <v>13587621.40503506</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>865.5571447256528</v>
+        <v>865.5571447256531</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>971.4113214462792</v>
+        <v>971.4113214462789</v>
       </c>
       <c r="E36" s="156" t="n">
         <v>1057.724240912187</v>
@@ -4522,13 +4522,13 @@
         <v>1367.867249153415</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1474.840076678237</v>
+        <v>1474.840076678236</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>865.5571447256528</v>
+        <v>865.5571447256531</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>971.4113214462792</v>
+        <v>971.4113214462789</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>1057.724240912187</v>
@@ -4537,13 +4537,13 @@
         <v>1367.867249153415</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>1474.840076678237</v>
+        <v>1474.840076678236</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>2890055.13782825</v>
+        <v>2890055.137828251</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>3463811.460964314</v>
+        <v>3463811.460964313</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>4012645.887468038</v>
@@ -4552,7 +4552,7 @@
         <v>4597660.105490743</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>5327904.332072279</v>
+        <v>5327904.332072278</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>1662.365164623265</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1792.368936662238</v>
+        <v>1792.368936662237</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>1051.909128077476</v>
@@ -4587,13 +4587,13 @@
         <v>1662.365164623265</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1792.368936662238</v>
+        <v>1792.368936662237</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>2890055.13782825</v>
+        <v>2890055.137828251</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>3463811.460964314</v>
+        <v>3463811.460964313</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>4012645.887468038</v>
@@ -4602,7 +4602,7 @@
         <v>4597660.105490743</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>5327904.332072279</v>
+        <v>5327904.332072278</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,34 +4612,34 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>515.0428935919281</v>
+        <v>515.0428935919279</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>567.7979772717214</v>
+        <v>567.797977271721</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>616.0454652239587</v>
+        <v>616.0454652239586</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>717.9239629115397</v>
+        <v>717.9239629115395</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>775.7401577380793</v>
+        <v>775.740157738079</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>515.0428935919281</v>
+        <v>515.0428935919279</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>567.7979772717214</v>
+        <v>567.797977271721</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>616.0454652239587</v>
+        <v>616.0454652239586</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>717.9239629115397</v>
+        <v>717.9239629115395</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>775.7401577380793</v>
+        <v>775.740157738079</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>10046330.26126956</v>
@@ -4651,7 +4651,7 @@
         <v>14054940.03195192</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>16359388.04785796</v>
+        <v>16359388.04785795</v>
       </c>
       <c r="Q37" s="166" t="n">
         <v>18915525.73710734</v>
@@ -4662,34 +4662,34 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>638.0584006983803</v>
+        <v>638.0584006983801</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>703.4782947979737</v>
+        <v>703.4782947979734</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>763.2723221696823</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>889.8891297573625</v>
+        <v>889.8891297573623</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>961.5395207708561</v>
+        <v>961.5395207708558</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>638.0584006983803</v>
+        <v>638.0584006983801</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>703.4782947979737</v>
+        <v>703.4782947979734</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>763.2723221696823</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>889.8891297573625</v>
+        <v>889.8891297573623</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>961.5395207708561</v>
+        <v>961.5395207708558</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>10046330.26126956</v>
@@ -4701,7 +4701,7 @@
         <v>14054940.03195192</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>16359388.04785796</v>
+        <v>16359388.04785795</v>
       </c>
       <c r="AH37" s="166" t="n">
         <v>18915525.73710734</v>
@@ -4720,7 +4720,7 @@
         <v>1317.392496827131</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>1424.142972323843</v>
+        <v>1424.142972323842</v>
       </c>
       <c r="F38" s="156" t="n">
         <v>1566.286456536697</v>
@@ -4735,7 +4735,7 @@
         <v>1317.392496827131</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>1424.142972323843</v>
+        <v>1424.142972323842</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>1566.286456536697</v>
@@ -4750,7 +4750,7 @@
         <v>135732.1912059643</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>162468.3891748899</v>
+        <v>162468.3891748898</v>
       </c>
       <c r="P38" s="159" t="n">
         <v>195685.1090677679</v>
@@ -4767,7 +4767,7 @@
         <v>1200.979813204907</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1348.290828309217</v>
+        <v>1348.290828309218</v>
       </c>
       <c r="V38" s="156" t="n">
         <v>1457.545046301587</v>
@@ -4776,13 +4776,13 @@
         <v>1603.022386220927</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1706.659926992532</v>
+        <v>1706.659926992531</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>1200.979813204907</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>1348.290828309217</v>
+        <v>1348.290828309218</v>
       </c>
       <c r="AA38" s="156" t="n">
         <v>1457.545046301587</v>
@@ -4791,7 +4791,7 @@
         <v>1603.022386220927</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1706.659926992532</v>
+        <v>1706.659926992531</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>110640.6185610632</v>
@@ -4800,7 +4800,7 @@
         <v>135732.1912059643</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>162468.3891748899</v>
+        <v>162468.3891748898</v>
       </c>
       <c r="AG38" s="159" t="n">
         <v>195685.1090677679</v>
@@ -4816,40 +4816,40 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>518.2101876455696</v>
+        <v>518.2101876455694</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>571.4031604450796</v>
+        <v>571.4031604450794</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>620.0661184008449</v>
+        <v>620.0661184008447</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>722.5499542964372</v>
+        <v>722.5499542964371</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>780.9136121777683</v>
+        <v>780.9136121777681</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>518.2101876455696</v>
+        <v>518.2101876455694</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>571.4031604450796</v>
+        <v>571.4031604450794</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>620.0661184008449</v>
+        <v>620.0661184008447</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>722.5499542964372</v>
+        <v>722.5499542964371</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>780.9136121777683</v>
+        <v>780.9136121777681</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>10156970.87983062</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>12240788.10307935</v>
+        <v>12240788.10307934</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>14217408.42112681</v>
@@ -4858,7 +4858,7 @@
         <v>16555073.15692572</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>19152781.25474411</v>
+        <v>19152781.2547441</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,40 +4866,40 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>641.3329080815005</v>
+        <v>641.3329080815002</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>707.2287438810126</v>
+        <v>707.2287438810123</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>767.4497262665312</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>894.5933042240339</v>
+        <v>894.5933042240337</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>966.7681309544749</v>
+        <v>966.7681309544746</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>641.3329080815005</v>
+        <v>641.3329080815002</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>707.2287438810126</v>
+        <v>707.2287438810123</v>
       </c>
       <c r="AA39" s="162" t="n">
         <v>767.4497262665312</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>894.5933042240339</v>
+        <v>894.5933042240337</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>966.7681309544749</v>
+        <v>966.7681309544746</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>10156970.87983062</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>12240788.10307935</v>
+        <v>12240788.10307934</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>14217408.42112681</v>
@@ -4908,7 +4908,7 @@
         <v>16555073.15692572</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>19152781.25474411</v>
+        <v>19152781.2547441</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>360.9019664303244</v>
+        <v>360.9019664303243</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>396.6549229391911</v>
+        <v>396.654922939191</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>428.5284069836077</v>
+        <v>428.5284069836076</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>461.5137005766636</v>
+        <v>461.5137005766634</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>496.9837786544927</v>
+        <v>496.9837786544925</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>360.9019664303244</v>
+        <v>360.9019664303243</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>396.6549229391911</v>
+        <v>396.654922939191</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>428.5284069836077</v>
+        <v>428.5284069836076</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>461.5137005766636</v>
+        <v>461.5137005766634</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>496.9837786544927</v>
+        <v>496.9837786544925</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>427.242025335316</v>
+        <v>427.2420253353159</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>481.7662852603256</v>
+        <v>481.7662852603255</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>536.2962316320555</v>
+        <v>536.2962316320554</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>589.2899543170867</v>
+        <v>589.2899543170865</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>647.450001775789</v>
+        <v>647.4500017757889</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>322.8679052853677</v>
+        <v>322.8679052853676</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>354.8529961119793</v>
+        <v>354.8529961119791</v>
       </c>
       <c r="V40" s="156" t="n">
         <v>383.3674570592407</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>412.8765582507658</v>
+        <v>412.8765582507657</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>444.6085821091286</v>
+        <v>444.6085821091285</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>322.8679052853677</v>
+        <v>322.8679052853676</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>354.8529961119793</v>
+        <v>354.8529961119791</v>
       </c>
       <c r="AA40" s="156" t="n">
         <v>383.3674570592407</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>412.8765582507658</v>
+        <v>412.8765582507657</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>444.6085821091286</v>
+        <v>444.6085821091285</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>427.242025335316</v>
+        <v>427.2420253353159</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>481.7662852603256</v>
+        <v>481.7662852603255</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>536.2962316320555</v>
+        <v>536.2962316320554</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>589.2899543170867</v>
+        <v>589.2899543170865</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>647.450001775789</v>
+        <v>647.4500017757889</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,40 +5020,40 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>518.200687032163</v>
+        <v>518.2006870321628</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>571.3932533804681</v>
+        <v>571.3932533804679</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>620.0556646226522</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>722.5354078189501</v>
+        <v>722.53540781895</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>780.8985314212907</v>
+        <v>780.8985314212904</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>518.200687032163</v>
+        <v>518.2006870321628</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>571.3932533804681</v>
+        <v>571.3932533804679</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>620.0556646226522</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>722.5354078189501</v>
+        <v>722.53540781895</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>780.8985314212907</v>
+        <v>780.8985314212904</v>
       </c>
       <c r="M41" s="182" t="n">
         <v>10157398.12185596</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>12241269.86936461</v>
+        <v>12241269.8693646</v>
       </c>
       <c r="O41" s="183" t="n">
         <v>14217944.71735844</v>
@@ -5062,7 +5062,7 @@
         <v>16555662.44688004</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>19153428.70474588</v>
+        <v>19153428.70474587</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,40 +5070,40 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>641.3063012086415</v>
+        <v>641.3063012086412</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>707.2011056401872</v>
+        <v>707.2011056401868</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>767.4207254341867</v>
+        <v>767.4207254341866</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>894.5561539860105</v>
+        <v>894.5561539860103</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>966.7297522619988</v>
+        <v>966.7297522619984</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>641.3063012086415</v>
+        <v>641.3063012086412</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>707.2011056401872</v>
+        <v>707.2011056401868</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>767.4207254341867</v>
+        <v>767.4207254341866</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>894.5561539860105</v>
+        <v>894.5561539860103</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>966.7297522619988</v>
+        <v>966.7297522619984</v>
       </c>
       <c r="AD41" s="188" t="n">
         <v>10157398.12185596</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>12241269.86936461</v>
+        <v>12241269.8693646</v>
       </c>
       <c r="AF41" s="189" t="n">
         <v>14217944.71735844</v>
@@ -5112,7 +5112,7 @@
         <v>16555662.44688004</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>19153428.70474588</v>
+        <v>19153428.70474587</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.3030479928119675</v>
+        <v>0.3030479928119676</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.1928950721971151</v>
+        <v>0.192895072197115</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.1410928334452031</v>
+        <v>0.141092833445203</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.09962689346713852</v>
+        <v>0.09962689346713847</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.05691410083355009</v>
+        <v>0.05691410083355006</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.3030479928119675</v>
+        <v>0.3030479928119676</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.1928950721971151</v>
+        <v>0.192895072197115</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.1410928334452031</v>
+        <v>0.141092833445203</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.09962689346713852</v>
+        <v>0.09962689346713847</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.05691410083355009</v>
+        <v>0.05691410083355006</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>4899.334229926491</v>
+        <v>4899.334229926493</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>3424.572171075029</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2683.74335472676</v>
+        <v>2683.743354726759</v>
       </c>
       <c r="P57" s="152" t="n">
         <v>1935.340812370471</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>1182.180555501657</v>
+        <v>1182.180555501656</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.376937976925713</v>
+        <v>0.3769379769257131</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.2399272722391336</v>
+        <v>0.2399272722391335</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.175494471037629</v>
+        <v>0.1754944710376289</v>
       </c>
       <c r="W57" s="149" t="n">
         <v>0.1239181930308886</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.0707910513700562</v>
+        <v>0.07079105137005616</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.376937976925713</v>
+        <v>0.3769379769257131</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.2399272722391336</v>
+        <v>0.2399272722391335</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.175494471037629</v>
+        <v>0.1754944710376289</v>
       </c>
       <c r="AB57" s="149" t="n">
         <v>0.1239181930308886</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>0.0707910513700562</v>
+        <v>0.07079105137005616</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>4899.334229926491</v>
+        <v>4899.334229926493</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>3424.572171075029</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2683.74335472676</v>
+        <v>2683.743354726759</v>
       </c>
       <c r="AG57" s="152" t="n">
         <v>1935.340812370471</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>1182.180555501657</v>
+        <v>1182.180555501656</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6439,7 +6439,7 @@
         <v>0.2986708527144198</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.1388708570600918</v>
+        <v>0.1388708570600917</v>
       </c>
       <c r="E58" s="156" t="n">
         <v>0.1024283644363289</v>
@@ -6454,7 +6454,7 @@
         <v>0.2986708527144198</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.1388708570600918</v>
+        <v>0.1388708570600917</v>
       </c>
       <c r="J58" s="156" t="n">
         <v>0.1024283644363289</v>
@@ -6469,10 +6469,10 @@
         <v>997.2481166225549</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>495.1789789339863</v>
+        <v>495.1789789339862</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>388.5783642067768</v>
+        <v>388.5783642067767</v>
       </c>
       <c r="P58" s="159" t="n">
         <v>279.1103535138191</v>
@@ -6519,10 +6519,10 @@
         <v>997.2481166225549</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>495.1789789339863</v>
+        <v>495.1789789339862</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>388.5783642067768</v>
+        <v>388.5783642067767</v>
       </c>
       <c r="AG58" s="159" t="n">
         <v>279.1103535138191</v>
@@ -6538,46 +6538,46 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.3022987255135205</v>
+        <v>0.3022987255135206</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.1838592725706117</v>
+        <v>0.1838592725706116</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.1346636740075248</v>
+        <v>0.1346636740075247</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.09718013608057262</v>
+        <v>0.09718013608057258</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.05548317283638752</v>
+        <v>0.05548317283638749</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.3022987255135205</v>
+        <v>0.3022987255135206</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.1838592725706117</v>
+        <v>0.1838592725706116</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.1346636740075248</v>
+        <v>0.1346636740075247</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.09718013608057262</v>
+        <v>0.09718013608057258</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.05548317283638752</v>
+        <v>0.05548317283638749</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>5896.582346549047</v>
+        <v>5896.582346549048</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>3919.751150009016</v>
+        <v>3919.751150009015</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>3072.321718933536</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>2214.451165884291</v>
+        <v>2214.45116588429</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>1352.892941398315</v>
@@ -6588,46 +6588,46 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.3745013157819415</v>
+        <v>0.3745013157819416</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.2277940618461789</v>
+        <v>0.2277940618461788</v>
       </c>
       <c r="V59" s="162" t="n">
         <v>0.1668465413250916</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.1204578077819344</v>
+        <v>0.1204578077819343</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.06877207901097145</v>
+        <v>0.0687720790109714</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.3745013157819415</v>
+        <v>0.3745013157819416</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.2277940618461789</v>
+        <v>0.2277940618461788</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0.1668465413250916</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.1204578077819344</v>
+        <v>0.1204578077819343</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.06877207901097145</v>
+        <v>0.0687720790109714</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>5896.582346549047</v>
+        <v>5896.582346549048</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>3919.751150009016</v>
+        <v>3919.751150009015</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>3072.321718933536</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>2214.451165884291</v>
+        <v>2214.45116588429</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>1352.892941398315</v>
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.3025320287172598</v>
+        <v>0.3025320287172599</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.1829749993556333</v>
+        <v>0.1829749993556332</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.133993660891592</v>
+        <v>0.1339936608915919</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.09665022760905249</v>
+        <v>0.09665022760905247</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.05516131050133898</v>
+        <v>0.05516131050133895</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.3025320287172598</v>
+        <v>0.3025320287172599</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.1829749993556333</v>
+        <v>0.1829749993556332</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.133993660891592</v>
+        <v>0.1339936608915919</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.09665022760905249</v>
+        <v>0.09665022760905247</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.05516131050133898</v>
+        <v>0.05516131050133895</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>5929.65765466375</v>
+        <v>5929.657654663752</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>3919.751150009016</v>
+        <v>3919.751150009015</v>
       </c>
       <c r="O61" s="165" t="n">
         <v>3072.321718933536</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>2214.451165884291</v>
+        <v>2214.45116588429</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>1352.892941398315</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.3744112917705488</v>
+        <v>0.3744112917705489</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.2264691340788469</v>
@@ -6804,10 +6804,10 @@
         <v>0.1196632093831876</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.06828949607583383</v>
+        <v>0.0682894960758338</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.3744112917705488</v>
+        <v>0.3744112917705489</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0.2264691340788469</v>
@@ -6819,19 +6819,19 @@
         <v>0.1196632093831876</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.06828949607583383</v>
+        <v>0.0682894960758338</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>5929.65765466375</v>
+        <v>5929.657654663752</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>3919.751150009016</v>
+        <v>3919.751150009015</v>
       </c>
       <c r="AF61" s="165" t="n">
         <v>3072.321718933536</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>2214.451165884291</v>
+        <v>2214.45116588429</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>1352.892941398315</v>
@@ -6946,46 +6946,46 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.3025137573273368</v>
+        <v>0.3025137573273369</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.1829646258882566</v>
+        <v>0.1829646258882565</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.1339863477624969</v>
+        <v>0.1339863477624968</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.09664484168912756</v>
+        <v>0.09664484168912751</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.05515838064264701</v>
+        <v>0.05515838064264698</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.3025137573273368</v>
+        <v>0.3025137573273369</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.1829646258882566</v>
+        <v>0.1829646258882565</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.1339863477624969</v>
+        <v>0.1339863477624968</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.09664484168912756</v>
+        <v>0.09664484168912751</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.05515838064264701</v>
+        <v>0.05515838064264698</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>5929.65765466375</v>
+        <v>5929.657654663752</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>3919.751150009016</v>
+        <v>3919.751150009015</v>
       </c>
       <c r="O63" s="183" t="n">
         <v>3072.321718933536</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>2214.451165884291</v>
+        <v>2214.45116588429</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>1352.892941398315</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.3743800107395104</v>
+        <v>0.3743800107395105</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0.2264513711978687</v>
@@ -7008,10 +7008,10 @@
         <v>0.1196539808962222</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.06828447680236648</v>
+        <v>0.06828447680236643</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.3743800107395104</v>
+        <v>0.3743800107395105</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0.2264513711978687</v>
@@ -7023,19 +7023,19 @@
         <v>0.1196539808962222</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.06828447680236648</v>
+        <v>0.06828447680236643</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>5929.65765466375</v>
+        <v>5929.657654663752</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>3919.751150009016</v>
+        <v>3919.751150009015</v>
       </c>
       <c r="AF63" s="189" t="n">
         <v>3072.321718933536</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>2214.451165884291</v>
+        <v>2214.45116588429</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>1352.892941398315</v>
@@ -7297,46 +7297,46 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>2.461414484727277</v>
+        <v>2.461414484727278</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>3.030080509686512</v>
+        <v>3.030080509686511</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>3.529116794758978</v>
+        <v>3.529116794758976</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>1.796678743494892</v>
+        <v>1.796678743494891</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>1.789797449334842</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>2.461414484727277</v>
+        <v>2.461414484727278</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>3.030080509686512</v>
+        <v>3.030080509686511</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>3.529116794758978</v>
+        <v>3.529116794758976</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>1.796678743494892</v>
+        <v>1.796678743494891</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>1.789797449334842</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>39793.34140168244</v>
+        <v>39793.34140168245</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>53794.68366607896</v>
+        <v>53794.68366607895</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>67127.74500816446</v>
+        <v>67127.74500816442</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>34902.07892662132</v>
+        <v>34902.0789266213</v>
       </c>
       <c r="Q68" s="153" t="n">
         <v>37176.44154790617</v>
@@ -7347,46 +7347,46 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>3.061563244949191</v>
+        <v>3.061563244949192</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>3.768882963537528</v>
+        <v>3.768882963537527</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>4.389595630076959</v>
+        <v>4.389595630076957</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>2.234749831121972</v>
+        <v>2.234749831121971</v>
       </c>
       <c r="X68" s="150" t="n">
         <v>2.226190721143212</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>3.061563244949191</v>
+        <v>3.061563244949192</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>3.768882963537528</v>
+        <v>3.768882963537527</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>4.389595630076959</v>
+        <v>4.389595630076957</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>2.234749831121972</v>
+        <v>2.234749831121971</v>
       </c>
       <c r="AC68" s="150" t="n">
         <v>2.226190721143212</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>39793.34140168244</v>
+        <v>39793.34140168245</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>53794.68366607896</v>
+        <v>53794.68366607895</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>67127.74500816446</v>
+        <v>67127.74500816442</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>34902.07892662132</v>
+        <v>34902.0789266213</v>
       </c>
       <c r="AH68" s="153" t="n">
         <v>37176.44154790617</v>
@@ -7408,7 +7408,7 @@
         <v>15.88077432076286</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.767485886511328</v>
+        <v>3.767485886511327</v>
       </c>
       <c r="G69" s="157" t="n">
         <v>4.07515297770954</v>
@@ -7423,7 +7423,7 @@
         <v>15.88077432076286</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>3.767485886511328</v>
+        <v>3.767485886511327</v>
       </c>
       <c r="L69" s="157" t="n">
         <v>4.07515297770954</v>
@@ -7432,10 +7432,10 @@
         <v>33345.90480761342</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>46623.44116502166</v>
+        <v>46623.44116502164</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>60246.25446142866</v>
+        <v>60246.25446142865</v>
       </c>
       <c r="P69" s="159" t="n">
         <v>12663.2314423297</v>
@@ -7458,7 +7458,7 @@
         <v>19.29985971549421</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>4.578614847180836</v>
+        <v>4.578614847180835</v>
       </c>
       <c r="X69" s="157" t="n">
         <v>4.952521785171654</v>
@@ -7473,7 +7473,7 @@
         <v>19.29985971549421</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>4.578614847180836</v>
+        <v>4.578614847180835</v>
       </c>
       <c r="AC69" s="157" t="n">
         <v>4.952521785171654</v>
@@ -7482,10 +7482,10 @@
         <v>33345.90480761342</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>46623.44116502166</v>
+        <v>46623.44116502164</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>60246.25446142866</v>
+        <v>60246.25446142865</v>
       </c>
       <c r="AG69" s="159" t="n">
         <v>12663.2314423297</v>
@@ -7504,10 +7504,10 @@
         <v>3.749612845995353</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>4.710197835979606</v>
+        <v>4.710197835979605</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>5.582960480962242</v>
+        <v>5.582960480962241</v>
       </c>
       <c r="F70" s="162" t="n">
         <v>2.087381020445072</v>
@@ -7519,10 +7519,10 @@
         <v>3.749612845995353</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>4.710197835979606</v>
+        <v>4.710197835979605</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>5.582960480962242</v>
+        <v>5.582960480962241</v>
       </c>
       <c r="K70" s="162" t="n">
         <v>2.087381020445072</v>
@@ -7531,7 +7531,7 @@
         <v>2.128378865549637</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>73139.24620929586</v>
+        <v>73139.24620929587</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>100418.1248311006</v>
@@ -7540,7 +7540,7 @@
         <v>127373.9994695931</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>47565.31036895102</v>
+        <v>47565.310368951</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>51898.0547906773</v>
@@ -7551,37 +7551,37 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>4.645189760931773</v>
+        <v>4.645189760931774</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>5.835741010803819</v>
+        <v>5.835741010803817</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>6.91721545151939</v>
+        <v>6.917215451519388</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>2.587373838620262</v>
+        <v>2.587373838620261</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>2.638151930108539</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>4.645189760931773</v>
+        <v>4.645189760931774</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>5.835741010803819</v>
+        <v>5.835741010803817</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>6.91721545151939</v>
+        <v>6.917215451519388</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>2.587373838620262</v>
+        <v>2.587373838620261</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>2.638151930108539</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>73139.24620929586</v>
+        <v>73139.24620929587</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>100418.1248311006</v>
@@ -7590,7 +7590,7 @@
         <v>127373.9994695931</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>47565.31036895102</v>
+        <v>47565.310368951</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>51898.0547906773</v>
@@ -7606,7 +7606,7 @@
         <v>7.21482233743582</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>8.783529712855097</v>
+        <v>8.783529712855096</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>10.17753349295959</v>
@@ -7621,7 +7621,7 @@
         <v>7.21482233743582</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>8.783529712855097</v>
+        <v>8.783529712855096</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>10.17753349295959</v>
@@ -7636,7 +7636,7 @@
         <v>680.2568495533</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>904.9753488955529</v>
+        <v>904.9753488955527</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>1161.068449241789</v>
@@ -7656,7 +7656,7 @@
         <v>7.384039918910862</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>8.98954000462782</v>
+        <v>8.989540004627816</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>10.41623896934031</v>
@@ -7671,7 +7671,7 @@
         <v>7.384039918910862</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>8.98954000462782</v>
+        <v>8.989540004627816</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>10.41623896934031</v>
@@ -7686,7 +7686,7 @@
         <v>680.2568495533</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>904.9753488955529</v>
+        <v>904.9753488955527</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>1161.068449241789</v>
@@ -7708,13 +7708,13 @@
         <v>3.766282190292825</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>4.729788570915509</v>
+        <v>4.729788570915507</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>5.605820574471775</v>
+        <v>5.605820574471773</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>2.123512245953507</v>
+        <v>2.123512245953506</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>2.170103559739575</v>
@@ -7723,28 +7723,28 @@
         <v>3.766282190292825</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>4.729788570915509</v>
+        <v>4.729788570915507</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>5.605820574471775</v>
+        <v>5.605820574471773</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>2.123512245953507</v>
+        <v>2.123512245953506</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>2.170103559739575</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>73819.50305884916</v>
+        <v>73819.50305884918</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>101323.1001799962</v>
+        <v>101323.1001799961</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>128535.0679188349</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>48653.93786595565</v>
+        <v>48653.93786595563</v>
       </c>
       <c r="Q72" s="166" t="n">
         <v>53224.22113237797</v>
@@ -7755,46 +7755,46 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>4.661121620804768</v>
+        <v>4.661121620804769</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>5.854084578786388</v>
+        <v>5.854084578786386</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>6.938268900215062</v>
+        <v>6.938268900215061</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.6291328722282</v>
+        <v>2.629132872228199</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>2.686580089923561</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>4.661121620804768</v>
+        <v>4.661121620804769</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>5.854084578786388</v>
+        <v>5.854084578786386</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>6.938268900215062</v>
+        <v>6.938268900215061</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>2.6291328722282</v>
+        <v>2.629132872228199</v>
       </c>
       <c r="AC72" s="163" t="n">
         <v>2.686580089923561</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>73819.50305884916</v>
+        <v>73819.50305884918</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>101323.1001799962</v>
+        <v>101323.1001799961</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>128535.0679188349</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>48653.93786595565</v>
+        <v>48653.93786595563</v>
       </c>
       <c r="AH72" s="166" t="n">
         <v>53224.22113237797</v>
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>51.94880105850979</v>
+        <v>51.94880105850978</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>54.05893804431466</v>
+        <v>54.05893804431464</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>56.43053948726752</v>
+        <v>56.4305394872675</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>58.93398235115023</v>
+        <v>58.93398235115021</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>61.53955761980597</v>
+        <v>61.53955761980595</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>51.94880105850979</v>
+        <v>51.94880105850978</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>54.05893804431466</v>
+        <v>54.05893804431464</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>56.43053948726752</v>
+        <v>56.4305394872675</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>58.93398235115023</v>
+        <v>58.93398235115021</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>61.53955761980597</v>
+        <v>61.53955761980595</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>61.49789428277896</v>
+        <v>61.49789428277894</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>65.65851640953964</v>
+        <v>65.65851640953963</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>70.62188919751856</v>
+        <v>70.62188919751853</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>75.25064526586968</v>
+        <v>75.25064526586966</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>80.17120155932571</v>
+        <v>80.1712015593257</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>46.4741180153294</v>
+        <v>46.47411801532939</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>48.36187583280732</v>
+        <v>48.36187583280729</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>50.48354338045637</v>
+        <v>50.48354338045635</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>52.72315809205827</v>
+        <v>52.72315809205826</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>55.05414186966163</v>
+        <v>55.05414186966162</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>46.4741180153294</v>
+        <v>46.47411801532939</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>48.36187583280732</v>
+        <v>48.36187583280729</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>50.48354338045637</v>
+        <v>50.48354338045635</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>52.72315809205827</v>
+        <v>52.72315809205826</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>55.05414186966163</v>
+        <v>55.05414186966162</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>61.49789428277896</v>
+        <v>61.49789428277894</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>65.65851640953964</v>
+        <v>65.65851640953963</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>70.62188919751856</v>
+        <v>70.62188919751853</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>75.25064526586968</v>
+        <v>75.25064526586966</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>80.17120155932571</v>
+        <v>80.1712015593257</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,37 +7909,37 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>3.769192168431161</v>
+        <v>3.769192168431162</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>4.732585206109301</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>5.60859449473156</v>
+        <v>5.608594494731558</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>2.126678059945411</v>
+        <v>2.12667805994541</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>2.173256931358818</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>3.769192168431161</v>
+        <v>3.769192168431162</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>4.732585206109301</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>5.60859449473156</v>
+        <v>5.608594494731558</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>2.126678059945411</v>
+        <v>2.12667805994541</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>2.173256931358818</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>73881.00095313194</v>
+        <v>73881.00095313195</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>101388.7586964057</v>
@@ -7948,7 +7948,7 @@
         <v>128605.6898080324</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>48729.18851122152</v>
+        <v>48729.1885112215</v>
       </c>
       <c r="Q74" s="184" t="n">
         <v>53304.39233393729</v>
@@ -7959,37 +7959,37 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>4.664614981359795</v>
+        <v>4.664614981359796</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>5.85741863505751</v>
+        <v>5.857418635057508</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>6.941556865596028</v>
+        <v>6.941556865596025</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>2.632996148678572</v>
+        <v>2.632996148678571</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>2.690429102267999</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>4.664614981359795</v>
+        <v>4.664614981359796</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>5.85741863505751</v>
+        <v>5.857418635057508</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>6.941556865596028</v>
+        <v>6.941556865596025</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>2.632996148678572</v>
+        <v>2.632996148678571</v>
       </c>
       <c r="AC74" s="187" t="n">
         <v>2.690429102267999</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>73881.00095313194</v>
+        <v>73881.00095313195</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>101388.7586964057</v>
@@ -7998,7 +7998,7 @@
         <v>128605.6898080324</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>48729.18851122152</v>
+        <v>48729.1885112215</v>
       </c>
       <c r="AH74" s="190" t="n">
         <v>53304.39233393729</v>
@@ -8260,40 +8260,40 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>445.4153840909526</v>
+        <v>445.4153840909524</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>489.9563218111653</v>
+        <v>489.9563218111651</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>531.6252142078655</v>
+        <v>531.6252142078653</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>607.3630064959406</v>
+        <v>607.3630064959403</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>655.9999634670116</v>
+        <v>655.9999634670113</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>445.4153840909526</v>
+        <v>445.4153840909523</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>489.9563218111653</v>
+        <v>489.956321811165</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>531.6252142078655</v>
+        <v>531.6252142078654</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>607.3630064959405</v>
+        <v>607.3630064959402</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>655.9999634670118</v>
+        <v>655.9999634670113</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>7200967.79907292</v>
+        <v>7200967.799072917</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>8698463.706746222</v>
+        <v>8698463.706746219</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>10112105.63284677</v>
@@ -8310,40 +8310,40 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>554.0177719474501</v>
+        <v>554.0177719474498</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>609.4188019917189</v>
+        <v>609.4188019917186</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>661.2475168266424</v>
+        <v>661.2475168266423</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>755.4519031912812</v>
+        <v>755.4519031912808</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>815.9476550172097</v>
+        <v>815.9476550172093</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>554.0177719474501</v>
+        <v>554.0177719474498</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>609.4188019917189</v>
+        <v>609.4188019917186</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>661.2475168266424</v>
+        <v>661.2475168266423</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>755.4519031912812</v>
+        <v>755.4519031912808</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>815.9476550172097</v>
+        <v>815.9476550172093</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>7200967.79907292</v>
+        <v>7200967.799072917</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>8698463.706746222</v>
+        <v>8698463.706746219</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>10112105.63284677</v>
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>875.842748275873</v>
+        <v>875.8427482758732</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>984.6255398223632</v>
+        <v>984.6255398223628</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1073.707443597387</v>
@@ -8377,10 +8377,10 @@
         <v>1478.962485284541</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>875.842748275873</v>
+        <v>875.8427482758732</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>984.6255398223632</v>
+        <v>984.625539822363</v>
       </c>
       <c r="J80" s="156" t="n">
         <v>1073.707443597387</v>
@@ -8392,10 +8392,10 @@
         <v>1478.962485284541</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>2924398.290752486</v>
+        <v>2924398.290752487</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>3510930.08110827</v>
+        <v>3510930.081108269</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>4073280.720293673</v>
@@ -8415,7 +8415,7 @@
         <v>1064.40919272161</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1196.612608871299</v>
+        <v>1196.612608871298</v>
       </c>
       <c r="V80" s="156" t="n">
         <v>1304.873592329725</v>
@@ -8424,13 +8424,13 @@
         <v>1667.044696745347</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1797.378888077995</v>
+        <v>1797.378888077994</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>1064.40919272161</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1196.612608871299</v>
+        <v>1196.612608871298</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>1304.873592329725</v>
@@ -8439,13 +8439,13 @@
         <v>1667.044696745347</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1797.378888077995</v>
+        <v>1797.378888077994</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>2924398.290752486</v>
+        <v>2924398.290752487</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>3510930.08110827</v>
+        <v>3510930.081108269</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>4073280.720293673</v>
@@ -8464,37 +8464,37 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>519.0948051634369</v>
+        <v>519.0948051634367</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>572.6920343802715</v>
+        <v>572.6920343802713</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>621.7630893789284</v>
+        <v>621.7630893789283</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>720.1085240680653</v>
+        <v>720.108524068065</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>777.9240197764653</v>
+        <v>777.924019776465</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>519.0948051634369</v>
+        <v>519.0948051634367</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>572.6920343802715</v>
+        <v>572.6920343802713</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>621.7630893789284</v>
+        <v>621.7630893789283</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>720.1085240680653</v>
+        <v>720.108524068065</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>777.9240197764653</v>
+        <v>777.924019776465</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>10125366.08982541</v>
+        <v>10125366.0898254</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>12209393.78785449</v>
@@ -8503,10 +8503,10 @@
         <v>14185386.35314044</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>16409167.80939279</v>
+        <v>16409167.80939278</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>18968776.68483942</v>
+        <v>18968776.68483941</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,37 +8514,37 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>643.078091775094</v>
+        <v>643.0780917750938</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>709.5418298706237</v>
+        <v>709.5418298706234</v>
       </c>
       <c r="V81" s="162" t="n">
         <v>770.3563841625268</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>892.5969614037648</v>
+        <v>892.5969614037643</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>964.2464447799757</v>
+        <v>964.2464447799754</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>643.078091775094</v>
+        <v>643.0780917750938</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>709.5418298706237</v>
+        <v>709.5418298706234</v>
       </c>
       <c r="AA81" s="162" t="n">
         <v>770.3563841625268</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>892.5969614037648</v>
+        <v>892.5969614037643</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>964.2464447799757</v>
+        <v>964.2464447799754</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>10125366.08982541</v>
+        <v>10125366.0898254</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>12209393.78785449</v>
@@ -8553,10 +8553,10 @@
         <v>14185386.35314044</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>16409167.80939279</v>
+        <v>16409167.80939278</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>18968776.68483942</v>
+        <v>18968776.68483941</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8569,7 +8569,7 @@
         <v>1181.022979092077</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1326.176026539986</v>
+        <v>1326.176026539987</v>
       </c>
       <c r="E82" s="156" t="n">
         <v>1434.320505816802</v>
@@ -8578,28 +8578,28 @@
         <v>1574.999958105084</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1676.869922441725</v>
+        <v>1676.869922441724</v>
       </c>
       <c r="H82" s="155" t="n">
         <v>1181.022979092077</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>1326.176026539986</v>
+        <v>1326.176026539987</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>1434.320505816802</v>
+        <v>1434.320505816801</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>1574.999958105084</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1676.869922441725</v>
+        <v>1676.869922441724</v>
       </c>
       <c r="M82" s="158" t="n">
         <v>111353.9507187312</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>136637.1665548598</v>
+        <v>136637.1665548599</v>
       </c>
       <c r="O82" s="159" t="n">
         <v>163629.4576241316</v>
@@ -8619,7 +8619,7 @@
         <v>1208.72287838848</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1357.280368313845</v>
+        <v>1357.280368313846</v>
       </c>
       <c r="V82" s="156" t="n">
         <v>1467.961285270927</v>
@@ -8634,7 +8634,7 @@
         <v>1208.72287838848</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>1357.280368313845</v>
+        <v>1357.280368313846</v>
       </c>
       <c r="AA82" s="156" t="n">
         <v>1467.961285270927</v>
@@ -8649,7 +8649,7 @@
         <v>111353.9507187312</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>136637.1665548598</v>
+        <v>136637.1665548599</v>
       </c>
       <c r="AF82" s="159" t="n">
         <v>163629.4576241316</v>
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>522.2790018645796</v>
+        <v>522.2790018645795</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>576.3159240153508</v>
+        <v>576.3159240153506</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>625.8059326362081</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>724.7701167699998</v>
+        <v>724.7701167699995</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>783.1388770480092</v>
+        <v>783.1388770480089</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>522.2790018645796</v>
+        <v>522.2790018645795</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>576.3159240153508</v>
+        <v>576.3159240153506</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>625.8059326362081</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>724.7701167699998</v>
+        <v>724.7701167699995</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>783.1388770480092</v>
+        <v>783.1388770480089</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>10236720.04054414</v>
+        <v>10236720.04054413</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>12346030.95440935</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>14349015.81076458</v>
+        <v>14349015.81076457</v>
       </c>
       <c r="P83" s="165" t="n">
         <v>16605941.54595756</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>19207358.36881788</v>
+        <v>19207358.36881787</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>646.3684409940757</v>
+        <v>646.3684409940755</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>713.3092975938779</v>
+        <v>713.3092975938775</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>774.5538378008156</v>
+        <v>774.5538378008155</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>897.3421003056453</v>
+        <v>897.342100305645</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>969.5230005404743</v>
+        <v>969.523000540474</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>646.3684409940757</v>
+        <v>646.3684409940755</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>713.3092975938779</v>
+        <v>713.3092975938775</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>774.5538378008156</v>
+        <v>774.5538378008155</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>897.3421003056453</v>
+        <v>897.342100305645</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>969.5230005404743</v>
+        <v>969.523000540474</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>10236720.04054414</v>
+        <v>10236720.04054413</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>12346030.95440935</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>14349015.81076458</v>
+        <v>14349015.81076457</v>
       </c>
       <c r="AG83" s="165" t="n">
         <v>16605941.54595756</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>19207358.36881788</v>
+        <v>19207358.36881787</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>412.8507674888342</v>
+        <v>412.8507674888341</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>450.7138609835058</v>
+        <v>450.7138609835056</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>484.9589464708753</v>
+        <v>484.9589464708751</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>520.4476829278138</v>
+        <v>520.4476829278136</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>558.5233362742986</v>
+        <v>558.5233362742985</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>412.8507674888342</v>
+        <v>412.8507674888341</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>450.7138609835058</v>
+        <v>450.7138609835056</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>484.9589464708752</v>
+        <v>484.9589464708751</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>520.4476829278138</v>
+        <v>520.4476829278137</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>558.5233362742986</v>
+        <v>558.5233362742985</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>488.739919618095</v>
+        <v>488.7399196180948</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>547.4248016698652</v>
+        <v>547.4248016698651</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>606.918120829574</v>
+        <v>606.9181208295739</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>664.5405995829564</v>
+        <v>664.5405995829562</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>727.6212033351147</v>
+        <v>727.6212033351146</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>369.3420233006971</v>
+        <v>369.342023300697</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>403.2148719447866</v>
+        <v>403.2148719447864</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>433.8510004396971</v>
+        <v>433.851000439697</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>465.5997163428241</v>
+        <v>465.599716342824</v>
       </c>
       <c r="X84" s="157" t="n">
         <v>499.6627239787902</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>369.3420233006971</v>
+        <v>369.342023300697</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>403.2148719447866</v>
+        <v>403.2148719447864</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>433.8510004396971</v>
+        <v>433.851000439697</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>465.5997163428241</v>
+        <v>465.599716342824</v>
       </c>
       <c r="AC84" s="157" t="n">
         <v>499.6627239787902</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>488.739919618095</v>
+        <v>488.7399196180948</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>547.4248016698652</v>
+        <v>547.4248016698651</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>606.918120829574</v>
+        <v>606.9181208295739</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>664.5405995829564</v>
+        <v>664.5405995829562</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>727.6212033351147</v>
+        <v>727.6212033351146</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,37 +8872,37 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>522.2723929579215</v>
+        <v>522.2723929579214</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>576.3088032124657</v>
+        <v>576.3088032124655</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>625.7982454651464</v>
+        <v>625.7982454651462</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>724.7587307205847</v>
+        <v>724.7587307205844</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>783.1269467332922</v>
+        <v>783.1269467332919</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>522.2723929579215</v>
+        <v>522.2723929579214</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>576.3088032124657</v>
+        <v>576.3088032124655</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>625.7982454651464</v>
+        <v>625.7982454651462</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>724.7587307205847</v>
+        <v>724.7587307205844</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>783.1269467332922</v>
+        <v>783.1269467332919</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>10237208.78046376</v>
+        <v>10237208.78046375</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>12346578.37921102</v>
@@ -8911,10 +8911,10 @@
         <v>14349622.7288854</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>16606606.08655715</v>
+        <v>16606606.08655714</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>19208085.99002122</v>
+        <v>19208085.99002121</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,37 +8922,37 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>646.3452962007407</v>
+        <v>646.3452962007404</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>713.2849756464426</v>
+        <v>713.2849756464423</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>774.5281124116015</v>
+        <v>774.5281124116013</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>897.3088041155852</v>
+        <v>897.3088041155848</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>969.4884658410692</v>
+        <v>969.4884658410688</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>646.3452962007407</v>
+        <v>646.3452962007404</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>713.2849756464426</v>
+        <v>713.2849756464423</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>774.5281124116015</v>
+        <v>774.5281124116013</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>897.3088041155852</v>
+        <v>897.3088041155848</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>969.4884658410692</v>
+        <v>969.4884658410688</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>10237208.78046376</v>
+        <v>10237208.78046375</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>12346578.37921102</v>
@@ -8961,10 +8961,10 @@
         <v>14349622.7288854</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>16606606.08655715</v>
+        <v>16606606.08655714</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>19208085.99002122</v>
+        <v>19208085.99002121</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
